--- a/Employee_Reports_wi48/Mabin Pauly Q0583.xlsx
+++ b/Employee_Reports_wi48/Mabin Pauly Q0583.xlsx
@@ -569,11 +569,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -618,11 +618,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -667,11 +667,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -716,11 +716,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -765,11 +765,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -814,11 +814,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -851,11 +851,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -900,11 +900,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -949,11 +949,11 @@
         </is>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-214</v>
+        <v>-217</v>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -998,11 +998,11 @@
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-125</v>
+        <v>-128</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
@@ -1047,11 +1047,11 @@
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-122</v>
+        <v>-125</v>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1070,9 +1070,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr"/>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
           <t>25-Mar-2025</t>
@@ -1084,11 +1096,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-110</v>
+        <v>-113</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1121,11 +1133,11 @@
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1308,7 +1320,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7639</v>
+        <v>7636</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1337,7 +1349,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7838</v>
+        <v>7835</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
